--- a/assets/downloads/tessallite-tpcds-live-dashboard.xlsx
+++ b/assets/downloads/tessallite-tpcds-live-dashboard.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" keepAlive="1" name="TessalliteTPCDS" type="5" refreshedVersion="8" minRefreshableVersion="3" saveData="1">
-    <dbPr connection="Provider=MSOLAP.8;Persist Security Info=True;User ID=admin@acme-demo.com;Initial Catalog=tpcds_retail;Data Source=https://sql.cloud.tessallite.io:8080/api/v1/xmla/acme-demo;Location=https://sql.cloud.tessallite.io:8080/api/v1/xmla/acme-demo;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="tpcds_retail" commandType="1"/>
+    <dbPr connection="Provider=MSOLAP.8;Persist Security Info=False;User ID=admin@acme-demo.com;Initial Catalog=tpcds_retail;Data Source=https://sql.cloud.tessallite.io:8080/api/v1/xmla/acme-demo;Location=https://sql.cloud.tessallite.io:8080/api/v1/xmla/acme-demo;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="tpcds_retail" commandType="1"/>
     <olapPr sendLocale="1" rowDrillCount="1000"/>
   </connection>
 </connections>
